--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294934950" windowHeight="6150"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
   <x:si>
     <x:t>Item_Equip_Hat_1</x:t>
   </x:si>
@@ -33,107 +31,113 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
     <x:t>옥수수다</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>Grade</x:t>
   </x:si>
   <x:si>
-    <x:t>Epic</x:t>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
   </x:si>
   <x:si>
     <x:t>Legend</x:t>
   </x:si>
   <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
+    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
     <x:t>지역에 나타나는 금화</x:t>
   </x:si>
   <x:si>
-    <x:t>ItemType</x:t>
+    <x:t>피자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
   </x:si>
   <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>착용하면 공격력이 강해진다.</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -165,6 +169,11 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -185,7 +194,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -215,7 +223,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -226,7 +233,7 @@
     </x:fill>
   </x:fills>
   <x:borders count="2">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color rgb="ff000000"/>
       </x:left>
@@ -234,29 +241,77 @@
         <x:color rgb="ff000000"/>
       </x:right>
       <x:top>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom>
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:left>
       <x:right style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:right>
       <x:top style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -264,22 +319,22 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -294,7 +349,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -306,19 +361,20 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="12">
+  <x:dxfs count="30">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -401,6 +457,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -435,6 +492,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -479,6 +537,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -522,6 +581,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -529,10 +589,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -541,10 +601,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -556,10 +616,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -568,10 +628,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -606,6 +666,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -626,6 +687,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -656,6 +718,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -681,6 +744,457 @@
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -709,7 +1223,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -904,9 +1418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:M35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
@@ -921,80 +1433,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.19999999999999928946">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1003,7 +1515,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1013,19 +1525,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1034,7 +1546,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1044,19 +1556,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1065,7 +1577,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1074,19 +1586,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1095,7 +1607,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1105,19 +1617,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1126,7 +1638,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1135,14 +1647,30 @@
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
-      <x:c r="D9" s="4"/>
-      <x:c r="E9" s="4"/>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
-      <x:c r="H9" s="4"/>
+      <x:c r="A9" s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G9" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="s">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -2305,7 +2833,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -16,121 +16,121 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Potato_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
+    <x:t>Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pizza_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -374,7 +374,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -457,7 +456,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -492,7 +490,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -537,7 +534,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -581,7 +577,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -666,7 +661,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -687,7 +681,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -718,7 +711,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1433,28 +1425,28 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
         <x:v>13</x:v>
@@ -1463,50 +1455,50 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1515,7 +1507,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1525,19 +1517,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1546,7 +1538,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1556,19 +1548,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1577,7 +1569,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1586,19 +1578,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1607,7 +1599,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1617,19 +1609,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1638,7 +1630,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1648,19 +1640,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>20</x:v>
@@ -1669,7 +1661,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -16,91 +16,94 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
     <x:t>옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>화폐</x:t>
   </x:si>
   <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
     <x:t>피자</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
+    <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Potato_1</x:t>
@@ -109,6 +112,9 @@
     <x:t>Item_Pizza_1</x:t>
   </x:si>
   <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_DummyBox_1</x:t>
   </x:si>
   <x:si>
@@ -116,12 +122,6 @@
   </x:si>
   <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
@@ -374,6 +374,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -456,6 +457,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -490,6 +492,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -534,6 +537,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -577,6 +581,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -661,6 +666,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -681,6 +687,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -711,6 +718,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1425,11 +1433,11 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
@@ -1437,68 +1445,68 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1517,19 +1525,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1548,19 +1556,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1578,19 +1586,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1599,7 +1607,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1609,19 +1617,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1640,19 +1648,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>20</x:v>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -14,7 +14,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+  <x:si>
+    <x:t>RandomItemBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeSp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
@@ -28,6 +79,9 @@
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
@@ -37,91 +91,58 @@
     <x:t>Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1,Item_Corn_1,Item_Potato_1,Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
   </x:si>
   <x:si>
     <x:t>Legend</x:t>
   </x:si>
   <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
     <x:t>Epic</x:t>
   </x:si>
   <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
+    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
     <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
-    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pizza_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+    <x:t>UseItemType</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
@@ -131,6 +152,15 @@
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -374,7 +404,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -457,7 +486,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -492,7 +520,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -537,7 +564,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -581,7 +607,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -666,7 +691,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -687,7 +711,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -718,7 +741,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1428,85 +1450,99 @@
     <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
     <x:col min="5" max="7" width="12.5703125" style="2"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <x:col min="9" max="16384" width="12.5703125" style="2"/>
+    <x:col min="9" max="9" width="12.5703125" style="2"/>
+    <x:col min="10" max="10" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="11" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="12.300000000000001">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
+      <x:c r="G3" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1515,29 +1551,33 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1546,7 +1586,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1556,19 +1596,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1577,28 +1617,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I6" s="4"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J6" s="2">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1607,29 +1652,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J7" s="4">
+        <x:v>200</x:v>
+      </x:c>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1638,29 +1687,33 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I8" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="4">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>20</x:v>
@@ -1669,10 +1722,14 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="4"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I9" s="4" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22785" windowHeight="8460"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,151 +16,151 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <x:si>
+    <x:t>Item_Equip_Hat_1,Item_Corn_1,Item_Potato_1,Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeSp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
     <x:t>RandomItemBox</x:t>
   </x:si>
   <x:si>
-    <x:t>StatChangeSp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pizza_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1,Item_Corn_1,Item_Potato_1,Item_Pizza_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플이 올려진 맛있는 피자다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
+    <x:t>mob_dog_1:2</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -404,6 +404,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -486,6 +487,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -520,6 +522,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -564,6 +567,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -607,6 +611,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -691,6 +696,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -711,6 +717,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -741,6 +748,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1457,92 +1465,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I3" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1551,13 +1559,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="s">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
@@ -1565,19 +1573,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1586,7 +1594,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1596,19 +1604,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1617,10 +1625,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J6" s="2">
         <x:v>700</x:v>
@@ -1631,19 +1639,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1652,10 +1660,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J7" s="4">
         <x:v>200</x:v>
@@ -1666,19 +1674,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1687,10 +1695,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J8" s="4">
         <x:v>20</x:v>
@@ -1701,19 +1709,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>20</x:v>
@@ -1722,13 +1730,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4"/>
